--- a/pages/WR_progressions/Women_F200.xlsx
+++ b/pages/WR_progressions/Women_F200.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207F83A0-0A5E-4170-BAD3-83A9FD54EB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F26424-C074-4208-A15A-00B997FAB9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{0C817B67-3DAE-42D7-8DC0-6EDE7BA5A428}"/>
   </bookViews>
@@ -83,10 +83,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -854,9 +855,33 @@
       <c r="K28" s="1"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>10.108000000000001</v>
+      </c>
+      <c r="B29">
+        <v>10.108000000000001</v>
+      </c>
+      <c r="C29" s="2">
+        <v>45513</v>
+      </c>
+      <c r="D29" s="3">
+        <v>45513</v>
+      </c>
       <c r="K29" s="1"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>10.029</v>
+      </c>
+      <c r="B30">
+        <v>10.029</v>
+      </c>
+      <c r="C30" s="2">
+        <v>45513</v>
+      </c>
+      <c r="D30" s="3">
+        <v>45513</v>
+      </c>
       <c r="K30" s="1"/>
     </row>
   </sheetData>

--- a/pages/WR_progressions/Women_F200.xlsx
+++ b/pages/WR_progressions/Women_F200.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F26424-C074-4208-A15A-00B997FAB9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA915913-3D72-4C6B-A96D-30EA3DFCD82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{0C817B67-3DAE-42D7-8DC0-6EDE7BA5A428}"/>
   </bookViews>
@@ -83,11 +83,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -856,37 +855,36 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29">
-        <v>10.108000000000001</v>
+        <v>10.029</v>
       </c>
       <c r="B29">
-        <v>10.108000000000001</v>
+        <v>10.029</v>
       </c>
       <c r="C29" s="2">
         <v>45513</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29">
         <v>45513</v>
       </c>
       <c r="K29" s="1"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30">
-        <v>10.029</v>
+        <v>9.9760000000000009</v>
       </c>
       <c r="B30">
-        <v>10.029</v>
+        <v>9.9760000000000009</v>
       </c>
       <c r="C30" s="2">
-        <v>45513</v>
-      </c>
-      <c r="D30" s="3">
-        <v>45513</v>
-      </c>
-      <c r="K30" s="1"/>
+        <v>45731</v>
+      </c>
+      <c r="D30">
+        <v>45731</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G4:K30">
-    <sortCondition ref="K4:K30"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G4:K29">
+    <sortCondition ref="K4:K29"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pages/WR_progressions/Women_F200.xlsx
+++ b/pages/WR_progressions/Women_F200.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA915913-3D72-4C6B-A96D-30EA3DFCD82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FEEF8E-9E1C-463D-9E2C-350C26DA9B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{0C817B67-3DAE-42D7-8DC0-6EDE7BA5A428}"/>
   </bookViews>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0A260E3-72A8-43E3-8C5E-C2B8DB5939E8}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="10.265625" bestFit="1" customWidth="1"/>
@@ -882,6 +882,20 @@
         <v>45731</v>
       </c>
     </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>9.7590000000000003</v>
+      </c>
+      <c r="B31">
+        <v>9.7590000000000003</v>
+      </c>
+      <c r="C31" s="2">
+        <v>46055</v>
+      </c>
+      <c r="D31">
+        <v>46055</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="G4:K29">
     <sortCondition ref="K4:K29"/>
